--- a/artfynd/A 29232-2025 artfynd.xlsx
+++ b/artfynd/A 29232-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2351,6 +2351,563 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129805635</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>607700</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6979421</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:13</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129805053</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80186</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>607694</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6979416</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129805049</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>607694</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6979416</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129805020</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91593</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>607728</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6979442</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129805111</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80186</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>607710</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6979462</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29232-2025 artfynd.xlsx
+++ b/artfynd/A 29232-2025 artfynd.xlsx
@@ -2703,7 +2703,7 @@
         <v>129805020</v>
       </c>
       <c r="B21" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29232-2025 artfynd.xlsx
+++ b/artfynd/A 29232-2025 artfynd.xlsx
@@ -2703,7 +2703,7 @@
         <v>129805020</v>
       </c>
       <c r="B21" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 29232-2025 artfynd.xlsx
+++ b/artfynd/A 29232-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2908,6 +2908,363 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129917166</v>
+      </c>
+      <c r="B23" t="n">
+        <v>56917</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>607659</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6979395</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Stöttes. Totalt 2 ex på olika platser.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129916476</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91599</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>607670</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6979437</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129917143</v>
+      </c>
+      <c r="B25" t="n">
+        <v>56917</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>607625</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6979416</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Stöttes</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29232-2025 artfynd.xlsx
+++ b/artfynd/A 29232-2025 artfynd.xlsx
@@ -2356,7 +2356,7 @@
         <v>129805635</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>129805053</v>
       </c>
       <c r="B19" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>129805049</v>
       </c>
       <c r="B20" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>129805020</v>
       </c>
       <c r="B21" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>129805111</v>
       </c>
       <c r="B22" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>129917166</v>
       </c>
       <c r="B23" t="n">
-        <v>56917</v>
+        <v>56918</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>129916476</v>
       </c>
       <c r="B24" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>129917143</v>
       </c>
       <c r="B25" t="n">
-        <v>56917</v>
+        <v>56918</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 29232-2025 artfynd.xlsx
+++ b/artfynd/A 29232-2025 artfynd.xlsx
@@ -2356,7 +2356,7 @@
         <v>129805635</v>
       </c>
       <c r="B18" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>129805053</v>
       </c>
       <c r="B19" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>129805049</v>
       </c>
       <c r="B20" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>129805020</v>
       </c>
       <c r="B21" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>129805111</v>
       </c>
       <c r="B22" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2913,7 +2913,7 @@
         <v>129917166</v>
       </c>
       <c r="B23" t="n">
-        <v>56918</v>
+        <v>56921</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>129916476</v>
       </c>
       <c r="B24" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>129917143</v>
       </c>
       <c r="B25" t="n">
-        <v>56918</v>
+        <v>56921</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 29232-2025 artfynd.xlsx
+++ b/artfynd/A 29232-2025 artfynd.xlsx
@@ -2475,7 +2475,7 @@
         <v>129805053</v>
       </c>
       <c r="B19" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>129805020</v>
       </c>
       <c r="B21" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>129805111</v>
       </c>
       <c r="B22" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>129916476</v>
       </c>
       <c r="B24" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 29232-2025 artfynd.xlsx
+++ b/artfynd/A 29232-2025 artfynd.xlsx
@@ -2475,7 +2475,7 @@
         <v>129805053</v>
       </c>
       <c r="B19" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2580,7 +2580,7 @@
         <v>129805049</v>
       </c>
       <c r="B20" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>129805020</v>
       </c>
       <c r="B21" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>129805111</v>
       </c>
       <c r="B22" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>129916476</v>
       </c>
       <c r="B24" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 29232-2025 artfynd.xlsx
+++ b/artfynd/A 29232-2025 artfynd.xlsx
@@ -2703,7 +2703,7 @@
         <v>129805020</v>
       </c>
       <c r="B21" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>129916476</v>
       </c>
       <c r="B24" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>130127210</v>
       </c>
       <c r="B27" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>130127284</v>
       </c>
       <c r="B28" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>130126081</v>
       </c>
       <c r="B29" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>130127479</v>
       </c>
       <c r="B31" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>130114283</v>
       </c>
       <c r="B33" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>130127255</v>
       </c>
       <c r="B34" t="n">
-        <v>91659</v>
+        <v>91661</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 29232-2025 artfynd.xlsx
+++ b/artfynd/A 29232-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2913,7 +2913,7 @@
         <v>129917166</v>
       </c>
       <c r="B23" t="n">
-        <v>56922</v>
+        <v>57007</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>129916476</v>
       </c>
       <c r="B24" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>129917143</v>
       </c>
       <c r="B25" t="n">
-        <v>56922</v>
+        <v>57007</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>130127319</v>
       </c>
       <c r="B26" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>130127210</v>
       </c>
       <c r="B27" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>130127284</v>
       </c>
       <c r="B28" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>130126081</v>
       </c>
       <c r="B29" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>130126046</v>
       </c>
       <c r="B30" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3781,10 +3781,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130127479</v>
+        <v>130127511</v>
       </c>
       <c r="B31" t="n">
-        <v>91661</v>
+        <v>57007</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3792,22 +3792,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3815,10 +3832,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>607689</v>
+        <v>607630</v>
       </c>
       <c r="R31" t="n">
-        <v>6979592</v>
+        <v>6979413</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3848,14 +3865,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På undersidan av grenar</t>
+          <t>Stöttes</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3864,7 +3891,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3883,10 +3909,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130127511</v>
+        <v>130114283</v>
       </c>
       <c r="B32" t="n">
-        <v>56922</v>
+        <v>91748</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3894,39 +3920,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -3934,10 +3951,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>607630</v>
+        <v>607618</v>
       </c>
       <c r="R32" t="n">
-        <v>6979413</v>
+        <v>6979482</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3964,27 +3981,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Stöttes</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3993,6 +3995,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4011,52 +4014,65 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130114283</v>
+        <v>130114120</v>
       </c>
       <c r="B33" t="n">
-        <v>91661</v>
+        <v>58198</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>607618</v>
+        <v>607648</v>
       </c>
       <c r="R33" t="n">
-        <v>6979482</v>
+        <v>6979427</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4086,18 +4102,32 @@
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rörde sig längs marken</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4116,10 +4146,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130127255</v>
+        <v>130114144</v>
       </c>
       <c r="B34" t="n">
-        <v>91661</v>
+        <v>57826</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4127,33 +4157,46 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>607732</v>
+        <v>607648</v>
       </c>
       <c r="R34" t="n">
-        <v>6979598</v>
+        <v>6979427</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4180,17 +4223,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På undersidan av grenar</t>
+          <t>ca 2,5 m över marken.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4199,7 +4242,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4218,65 +4260,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130114120</v>
+        <v>130266832</v>
       </c>
       <c r="B35" t="n">
-        <v>58113</v>
+        <v>92026</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103015</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>607648</v>
+        <v>607828</v>
       </c>
       <c r="R35" t="n">
-        <v>6979427</v>
+        <v>6979513</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4303,27 +4328,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:08</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rörde sig längs marken</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4332,6 +4342,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4350,10 +4361,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130114144</v>
+        <v>130266710</v>
       </c>
       <c r="B36" t="n">
-        <v>57741</v>
+        <v>91728</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4361,46 +4372,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>607648</v>
+        <v>607751</v>
       </c>
       <c r="R36" t="n">
-        <v>6979427</v>
+        <v>6979617</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4427,17 +4429,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>ca 2,5 m över marken.</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4446,6 +4443,7 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4461,6 +4459,1085 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>130266869</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91728</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>607736</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6979447</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>130266801</v>
+      </c>
+      <c r="B38" t="n">
+        <v>91728</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>607828</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6979513</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>130238674</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57930</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>607654</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6979404</v>
+      </c>
+      <c r="S39" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>130266667</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92026</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>658</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>607751</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6979617</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>130266607</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91748</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>607717</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6979647</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>130275381</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91728</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>607764</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6979498</v>
+      </c>
+      <c r="S42" t="n">
+        <v>25</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>130276095</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57985</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>607828</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6979513</v>
+      </c>
+      <c r="S43" t="n">
+        <v>25</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>130275701</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57985</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>607706</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6979662</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Sannolikt samma fåglar som observerades tidigare. Nyfikna.</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>130127479</v>
+      </c>
+      <c r="B45" t="n">
+        <v>91692</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>607689</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6979592</v>
+      </c>
+      <c r="S45" t="n">
+        <v>25</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-12-14</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-12-14</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På undersidan av grenar. Bedömd utifrån foto. Extern input.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>130127255</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91692</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>607732</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6979598</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-12-14</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-12-14</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På undersidan av grenar. Bedömd utifrån foto. Extern input.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29232-2025 artfynd.xlsx
+++ b/artfynd/A 29232-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4880,10 +4880,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130266607</v>
+        <v>130275381</v>
       </c>
       <c r="B41" t="n">
-        <v>91748</v>
+        <v>91728</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4891,19 +4891,23 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
@@ -4914,10 +4918,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>607717</v>
+        <v>607764</v>
       </c>
       <c r="R41" t="n">
-        <v>6979647</v>
+        <v>6979498</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4977,10 +4981,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130275381</v>
+        <v>130276095</v>
       </c>
       <c r="B42" t="n">
-        <v>91728</v>
+        <v>57985</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4988,37 +4992,50 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>607764</v>
+        <v>607828</v>
       </c>
       <c r="R42" t="n">
-        <v>6979498</v>
+        <v>6979513</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5048,18 +5065,27 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5078,7 +5104,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130276095</v>
+        <v>130275701</v>
       </c>
       <c r="B43" t="n">
         <v>57985</v>
@@ -5129,10 +5155,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>607828</v>
+        <v>607706</v>
       </c>
       <c r="R43" t="n">
-        <v>6979513</v>
+        <v>6979662</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5164,7 +5190,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5174,7 +5200,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Sannolikt samma fåglar som observerades tidigare. Nyfikna.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5201,61 +5232,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130275701</v>
+        <v>130127479</v>
       </c>
       <c r="B44" t="n">
-        <v>57985</v>
+        <v>91692</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>607706</v>
+        <v>607689</v>
       </c>
       <c r="R44" t="n">
-        <v>6979662</v>
+        <v>6979592</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5282,27 +5300,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:25</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:25</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Sannolikt samma fåglar som observerades tidigare. Nyfikna.</t>
+          <t>På undersidan av grenar. Bedömd utifrån foto. Extern input.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5311,6 +5319,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5329,7 +5338,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130127479</v>
+        <v>130127255</v>
       </c>
       <c r="B45" t="n">
         <v>91692</v>
@@ -5367,10 +5376,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>607689</v>
+        <v>607732</v>
       </c>
       <c r="R45" t="n">
-        <v>6979592</v>
+        <v>6979598</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5435,32 +5444,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130127255</v>
+        <v>130306278</v>
       </c>
       <c r="B46" t="n">
-        <v>91692</v>
+        <v>92026</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5473,10 +5482,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>607732</v>
+        <v>607751</v>
       </c>
       <c r="R46" t="n">
-        <v>6979598</v>
+        <v>6979524</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5503,17 +5512,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På undersidan av grenar. Bedömd utifrån foto. Extern input.</t>
+          <t>Samma låga som ulltickan</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5538,6 +5547,412 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>130306274</v>
+      </c>
+      <c r="B47" t="n">
+        <v>91728</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>607751</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6979524</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Samma låga som rosentickan</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>130266607</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91748</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>607717</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6979647</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>130306283</v>
+      </c>
+      <c r="B49" t="n">
+        <v>92181</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>607751</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6979524</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Misstänkt rynkskinn, behövs verifiering. Växte på samma låga som ulltickan och rosentickan.</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>130306215</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91748</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>607702</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6979571</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29232-2025 artfynd.xlsx
+++ b/artfynd/A 29232-2025 artfynd.xlsx
@@ -5753,34 +5753,30 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130306283</v>
+        <v>130306215</v>
       </c>
       <c r="B49" t="n">
-        <v>92181</v>
+        <v>91748</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1209</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
@@ -5791,10 +5787,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>607751</v>
+        <v>607702</v>
       </c>
       <c r="R49" t="n">
-        <v>6979524</v>
+        <v>6979571</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5827,11 +5823,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Misstänkt rynkskinn, behövs verifiering. Växte på samma låga som ulltickan och rosentickan.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5859,30 +5850,34 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130306215</v>
+        <v>130306283</v>
       </c>
       <c r="B50" t="n">
-        <v>91748</v>
+        <v>92181</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>1209</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr"/>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
@@ -5893,10 +5888,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>607702</v>
+        <v>607751</v>
       </c>
       <c r="R50" t="n">
-        <v>6979571</v>
+        <v>6979524</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5929,6 +5924,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Misstänkt rynkskinn, behövs verifiering. Växte på samma låga som ullticka och rosenticka.</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 29232-2025 artfynd.xlsx
+++ b/artfynd/A 29232-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Misstänkt rynkskinn, behövs verifiering. Växte på samma låga som ullticka och rosenticka.</t>
+          <t>Artbestämd efter extern bedömning av foton. Rynkskinn (ungt exemplar) utifrån vit fransig kant och begynnande åsar/rynkor. På grov granlåga tillsammans med ullticka och rosenticka. Ej mikroskoperad.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5953,6 +5953,208 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>130349421</v>
+      </c>
+      <c r="B51" t="n">
+        <v>91728</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>607743</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6979551</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>130349427</v>
+      </c>
+      <c r="B52" t="n">
+        <v>92026</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>658</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>607743</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6979551</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29232-2025 artfynd.xlsx
+++ b/artfynd/A 29232-2025 artfynd.xlsx
@@ -2913,7 +2913,7 @@
         <v>129917166</v>
       </c>
       <c r="B23" t="n">
-        <v>57007</v>
+        <v>56922</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>129916476</v>
       </c>
       <c r="B24" t="n">
-        <v>91728</v>
+        <v>91641</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>129917143</v>
       </c>
       <c r="B25" t="n">
-        <v>57007</v>
+        <v>56922</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 29232-2025 artfynd.xlsx
+++ b/artfynd/A 29232-2025 artfynd.xlsx
@@ -3380,7 +3380,7 @@
         <v>130127210</v>
       </c>
       <c r="B27" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>130127284</v>
       </c>
       <c r="B28" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>130126081</v>
       </c>
       <c r="B29" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>130126046</v>
       </c>
       <c r="B30" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>130114283</v>
       </c>
       <c r="B32" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>130266832</v>
       </c>
       <c r="B35" t="n">
-        <v>92026</v>
+        <v>92029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>130266710</v>
       </c>
       <c r="B36" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>130266869</v>
       </c>
       <c r="B37" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>130266801</v>
       </c>
       <c r="B38" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>130266667</v>
       </c>
       <c r="B40" t="n">
-        <v>92026</v>
+        <v>92029</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>130275381</v>
       </c>
       <c r="B41" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>130127479</v>
       </c>
       <c r="B44" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>130127255</v>
       </c>
       <c r="B45" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>130306278</v>
       </c>
       <c r="B46" t="n">
-        <v>92026</v>
+        <v>92029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>130266607</v>
       </c>
       <c r="B47" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>130306274</v>
       </c>
       <c r="B48" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>130306215</v>
       </c>
       <c r="B49" t="n">
-        <v>91748</v>
+        <v>91751</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>130306283</v>
       </c>
       <c r="B50" t="n">
-        <v>92181</v>
+        <v>92184</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>130349421</v>
       </c>
       <c r="B51" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         <v>130349427</v>
       </c>
       <c r="B52" t="n">
-        <v>92026</v>
+        <v>92029</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 29232-2025 artfynd.xlsx
+++ b/artfynd/A 29232-2025 artfynd.xlsx
@@ -3270,7 +3270,7 @@
         <v>130127319</v>
       </c>
       <c r="B26" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>130127210</v>
       </c>
       <c r="B27" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>130127284</v>
       </c>
       <c r="B28" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>130126081</v>
       </c>
       <c r="B29" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
         <v>130126046</v>
       </c>
       <c r="B30" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>130127511</v>
       </c>
       <c r="B31" t="n">
-        <v>57007</v>
+        <v>57033</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3912,7 +3912,7 @@
         <v>130114283</v>
       </c>
       <c r="B32" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>130114120</v>
       </c>
       <c r="B33" t="n">
-        <v>58198</v>
+        <v>58224</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4149,7 +4149,7 @@
         <v>130114144</v>
       </c>
       <c r="B34" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>130266832</v>
       </c>
       <c r="B35" t="n">
-        <v>92029</v>
+        <v>92055</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>130266710</v>
       </c>
       <c r="B36" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>130266869</v>
       </c>
       <c r="B37" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>130266801</v>
       </c>
       <c r="B38" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>130238674</v>
       </c>
       <c r="B39" t="n">
-        <v>57930</v>
+        <v>57956</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>130266667</v>
       </c>
       <c r="B40" t="n">
-        <v>92029</v>
+        <v>92055</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>130275381</v>
       </c>
       <c r="B41" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>130276095</v>
       </c>
       <c r="B42" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>130275701</v>
       </c>
       <c r="B43" t="n">
-        <v>57985</v>
+        <v>58011</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>130127479</v>
       </c>
       <c r="B44" t="n">
-        <v>91695</v>
+        <v>91721</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>130127255</v>
       </c>
       <c r="B45" t="n">
-        <v>91695</v>
+        <v>91721</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>130306278</v>
       </c>
       <c r="B46" t="n">
-        <v>92029</v>
+        <v>92055</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5550,10 +5550,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130266607</v>
+        <v>130306274</v>
       </c>
       <c r="B47" t="n">
-        <v>91751</v>
+        <v>91757</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5561,19 +5561,23 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -5584,10 +5588,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>607717</v>
+        <v>607751</v>
       </c>
       <c r="R47" t="n">
-        <v>6979647</v>
+        <v>6979524</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5614,12 +5618,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Samma låga som rosentickan</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5647,10 +5656,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130306274</v>
+        <v>130266607</v>
       </c>
       <c r="B48" t="n">
-        <v>91731</v>
+        <v>91777</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5658,23 +5667,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
@@ -5685,10 +5690,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>607751</v>
+        <v>607717</v>
       </c>
       <c r="R48" t="n">
-        <v>6979524</v>
+        <v>6979647</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5715,17 +5720,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Samma låga som rosentickan</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5756,7 +5756,7 @@
         <v>130306215</v>
       </c>
       <c r="B49" t="n">
-        <v>91751</v>
+        <v>91777</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>130306283</v>
       </c>
       <c r="B50" t="n">
-        <v>92184</v>
+        <v>92210</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>130349421</v>
       </c>
       <c r="B51" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         <v>130349427</v>
       </c>
       <c r="B52" t="n">
-        <v>92029</v>
+        <v>92055</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 29232-2025 artfynd.xlsx
+++ b/artfynd/A 29232-2025 artfynd.xlsx
@@ -4263,7 +4263,7 @@
         <v>130266832</v>
       </c>
       <c r="B35" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>130266710</v>
       </c>
       <c r="B36" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>130266869</v>
       </c>
       <c r="B37" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>130266801</v>
       </c>
       <c r="B38" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>130266667</v>
       </c>
       <c r="B40" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>130275381</v>
       </c>
       <c r="B41" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>130127479</v>
       </c>
       <c r="B44" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>130127255</v>
       </c>
       <c r="B45" t="n">
-        <v>91721</v>
+        <v>91722</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>130306278</v>
       </c>
       <c r="B46" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>130306274</v>
       </c>
       <c r="B47" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>130266607</v>
       </c>
       <c r="B48" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>130306215</v>
       </c>
       <c r="B49" t="n">
-        <v>91777</v>
+        <v>91778</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>130306283</v>
       </c>
       <c r="B50" t="n">
-        <v>92210</v>
+        <v>92211</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>130349421</v>
       </c>
       <c r="B51" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         <v>130349427</v>
       </c>
       <c r="B52" t="n">
-        <v>92055</v>
+        <v>92056</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 29232-2025 artfynd.xlsx
+++ b/artfynd/A 29232-2025 artfynd.xlsx
@@ -4263,7 +4263,7 @@
         <v>130266832</v>
       </c>
       <c r="B35" t="n">
-        <v>92056</v>
+        <v>92057</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>130266710</v>
       </c>
       <c r="B36" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>130266869</v>
       </c>
       <c r="B37" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>130266801</v>
       </c>
       <c r="B38" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>130266667</v>
       </c>
       <c r="B40" t="n">
-        <v>92056</v>
+        <v>92057</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>130275381</v>
       </c>
       <c r="B41" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>130127479</v>
       </c>
       <c r="B44" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>130127255</v>
       </c>
       <c r="B45" t="n">
-        <v>91722</v>
+        <v>91723</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>130306278</v>
       </c>
       <c r="B46" t="n">
-        <v>92056</v>
+        <v>92057</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>130306274</v>
       </c>
       <c r="B47" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>130266607</v>
       </c>
       <c r="B48" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>130306215</v>
       </c>
       <c r="B49" t="n">
-        <v>91778</v>
+        <v>91779</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>130306283</v>
       </c>
       <c r="B50" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>130349421</v>
       </c>
       <c r="B51" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         <v>130349427</v>
       </c>
       <c r="B52" t="n">
-        <v>92056</v>
+        <v>92057</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 29232-2025 artfynd.xlsx
+++ b/artfynd/A 29232-2025 artfynd.xlsx
@@ -4149,7 +4149,7 @@
         <v>130114144</v>
       </c>
       <c r="B34" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4263,7 +4263,7 @@
         <v>130266832</v>
       </c>
       <c r="B35" t="n">
-        <v>92057</v>
+        <v>92059</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>130266710</v>
       </c>
       <c r="B36" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>130266869</v>
       </c>
       <c r="B37" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>130266801</v>
       </c>
       <c r="B38" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>130238674</v>
       </c>
       <c r="B39" t="n">
-        <v>57956</v>
+        <v>57958</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>130266667</v>
       </c>
       <c r="B40" t="n">
-        <v>92057</v>
+        <v>92059</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>130275381</v>
       </c>
       <c r="B41" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>130276095</v>
       </c>
       <c r="B42" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>130275701</v>
       </c>
       <c r="B43" t="n">
-        <v>58011</v>
+        <v>58013</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>130127479</v>
       </c>
       <c r="B44" t="n">
-        <v>91723</v>
+        <v>91725</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>130127255</v>
       </c>
       <c r="B45" t="n">
-        <v>91723</v>
+        <v>91725</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>130306278</v>
       </c>
       <c r="B46" t="n">
-        <v>92057</v>
+        <v>92059</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>130306274</v>
       </c>
       <c r="B47" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>130266607</v>
       </c>
       <c r="B48" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>130306215</v>
       </c>
       <c r="B49" t="n">
-        <v>91779</v>
+        <v>91781</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>130306283</v>
       </c>
       <c r="B50" t="n">
-        <v>92212</v>
+        <v>92214</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>130349421</v>
       </c>
       <c r="B51" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         <v>130349427</v>
       </c>
       <c r="B52" t="n">
-        <v>92057</v>
+        <v>92059</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 29232-2025 artfynd.xlsx
+++ b/artfynd/A 29232-2025 artfynd.xlsx
@@ -5853,7 +5853,7 @@
         <v>130306283</v>
       </c>
       <c r="B50" t="n">
-        <v>92214</v>
+        <v>92220</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 29232-2025 artfynd.xlsx
+++ b/artfynd/A 29232-2025 artfynd.xlsx
@@ -5550,10 +5550,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130306274</v>
+        <v>130266607</v>
       </c>
       <c r="B47" t="n">
-        <v>91761</v>
+        <v>91781</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5561,23 +5561,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -5588,10 +5584,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>607751</v>
+        <v>607717</v>
       </c>
       <c r="R47" t="n">
-        <v>6979524</v>
+        <v>6979647</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5618,17 +5614,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Samma låga som rosentickan</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5656,10 +5647,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130266607</v>
+        <v>130306274</v>
       </c>
       <c r="B48" t="n">
-        <v>91781</v>
+        <v>91761</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5667,19 +5658,23 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
@@ -5690,10 +5685,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>607717</v>
+        <v>607751</v>
       </c>
       <c r="R48" t="n">
-        <v>6979647</v>
+        <v>6979524</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5720,12 +5715,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Samma låga som rosentickan</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 29232-2025 artfynd.xlsx
+++ b/artfynd/A 29232-2025 artfynd.xlsx
@@ -4263,7 +4263,7 @@
         <v>130266832</v>
       </c>
       <c r="B35" t="n">
-        <v>92059</v>
+        <v>92072</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>130266710</v>
       </c>
       <c r="B36" t="n">
-        <v>91761</v>
+        <v>91774</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
         <v>130266869</v>
       </c>
       <c r="B37" t="n">
-        <v>91761</v>
+        <v>91774</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         <v>130266801</v>
       </c>
       <c r="B38" t="n">
-        <v>91761</v>
+        <v>91774</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>130238674</v>
       </c>
       <c r="B39" t="n">
-        <v>57958</v>
+        <v>57966</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4782,7 +4782,7 @@
         <v>130266667</v>
       </c>
       <c r="B40" t="n">
-        <v>92059</v>
+        <v>92072</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4883,7 +4883,7 @@
         <v>130275381</v>
       </c>
       <c r="B41" t="n">
-        <v>91761</v>
+        <v>91774</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4984,7 +4984,7 @@
         <v>130276095</v>
       </c>
       <c r="B42" t="n">
-        <v>58013</v>
+        <v>58021</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5107,7 +5107,7 @@
         <v>130275701</v>
       </c>
       <c r="B43" t="n">
-        <v>58013</v>
+        <v>58021</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5235,7 +5235,7 @@
         <v>130127479</v>
       </c>
       <c r="B44" t="n">
-        <v>91725</v>
+        <v>91737</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>130127255</v>
       </c>
       <c r="B45" t="n">
-        <v>91725</v>
+        <v>91737</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>130306278</v>
       </c>
       <c r="B46" t="n">
-        <v>92059</v>
+        <v>92072</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5550,10 +5550,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130266607</v>
+        <v>130306274</v>
       </c>
       <c r="B47" t="n">
-        <v>91781</v>
+        <v>91774</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5561,19 +5561,23 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -5584,10 +5588,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>607717</v>
+        <v>607751</v>
       </c>
       <c r="R47" t="n">
-        <v>6979647</v>
+        <v>6979524</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5614,12 +5618,17 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Samma låga som rosentickan</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5647,10 +5656,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130306274</v>
+        <v>130266607</v>
       </c>
       <c r="B48" t="n">
-        <v>91761</v>
+        <v>91794</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5658,23 +5667,19 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
@@ -5685,10 +5690,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>607751</v>
+        <v>607717</v>
       </c>
       <c r="R48" t="n">
-        <v>6979524</v>
+        <v>6979647</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5715,17 +5720,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Samma låga som rosentickan</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5756,7 +5756,7 @@
         <v>130306215</v>
       </c>
       <c r="B49" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>130306283</v>
       </c>
       <c r="B50" t="n">
-        <v>92220</v>
+        <v>92233</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>130349421</v>
       </c>
       <c r="B51" t="n">
-        <v>91761</v>
+        <v>91774</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         <v>130349427</v>
       </c>
       <c r="B52" t="n">
-        <v>92059</v>
+        <v>92072</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 29232-2025 artfynd.xlsx
+++ b/artfynd/A 29232-2025 artfynd.xlsx
@@ -5235,7 +5235,7 @@
         <v>130127479</v>
       </c>
       <c r="B44" t="n">
-        <v>91737</v>
+        <v>91738</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>130127255</v>
       </c>
       <c r="B45" t="n">
-        <v>91737</v>
+        <v>91738</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>130306278</v>
       </c>
       <c r="B46" t="n">
-        <v>92072</v>
+        <v>92073</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>130306274</v>
       </c>
       <c r="B47" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>130266607</v>
       </c>
       <c r="B48" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>130306215</v>
       </c>
       <c r="B49" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>130306283</v>
       </c>
       <c r="B50" t="n">
-        <v>92233</v>
+        <v>92234</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>130349421</v>
       </c>
       <c r="B51" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         <v>130349427</v>
       </c>
       <c r="B52" t="n">
-        <v>92072</v>
+        <v>92073</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 29232-2025 artfynd.xlsx
+++ b/artfynd/A 29232-2025 artfynd.xlsx
@@ -5235,7 +5235,7 @@
         <v>130127479</v>
       </c>
       <c r="B44" t="n">
-        <v>91738</v>
+        <v>91739</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5341,7 +5341,7 @@
         <v>130127255</v>
       </c>
       <c r="B45" t="n">
-        <v>91738</v>
+        <v>91739</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>130306278</v>
       </c>
       <c r="B46" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5553,7 +5553,7 @@
         <v>130306274</v>
       </c>
       <c r="B47" t="n">
-        <v>91775</v>
+        <v>91776</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>130266607</v>
       </c>
       <c r="B48" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>130306215</v>
       </c>
       <c r="B49" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>130306283</v>
       </c>
       <c r="B50" t="n">
-        <v>92234</v>
+        <v>92235</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>130349421</v>
       </c>
       <c r="B51" t="n">
-        <v>91775</v>
+        <v>91776</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         <v>130349427</v>
       </c>
       <c r="B52" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>

--- a/artfynd/A 29232-2025 artfynd.xlsx
+++ b/artfynd/A 29232-2025 artfynd.xlsx
@@ -5550,10 +5550,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130306274</v>
+        <v>130266607</v>
       </c>
       <c r="B47" t="n">
-        <v>91776</v>
+        <v>91796</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5561,23 +5561,19 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
@@ -5588,10 +5584,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>607751</v>
+        <v>607717</v>
       </c>
       <c r="R47" t="n">
-        <v>6979524</v>
+        <v>6979647</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5618,17 +5614,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Samma låga som rosentickan</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5656,10 +5647,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130266607</v>
+        <v>130306274</v>
       </c>
       <c r="B48" t="n">
-        <v>91796</v>
+        <v>91776</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5667,19 +5658,23 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
@@ -5690,10 +5685,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>607717</v>
+        <v>607751</v>
       </c>
       <c r="R48" t="n">
-        <v>6979647</v>
+        <v>6979524</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5720,12 +5715,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Samma låga som rosentickan</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 29232-2025 artfynd.xlsx
+++ b/artfynd/A 29232-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111836259</v>
+        <v>130266667</v>
       </c>
       <c r="B2" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Granåsen, Ång</t>
+          <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607667</v>
+        <v>607751</v>
       </c>
       <c r="R2" t="n">
-        <v>6979558</v>
+        <v>6979617</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,33 +757,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111836231</v>
+        <v>130266832</v>
       </c>
       <c r="B3" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +787,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Granåsen, Ång</t>
+          <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607765</v>
+        <v>607828</v>
       </c>
       <c r="R3" t="n">
-        <v>6979740</v>
+        <v>6979513</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -861,33 +858,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111836232</v>
+        <v>130306278</v>
       </c>
       <c r="B4" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,37 +888,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Granåsen, Ång</t>
+          <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607753</v>
+        <v>607751</v>
       </c>
       <c r="R4" t="n">
-        <v>6979689</v>
+        <v>6979524</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +945,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Samma låga som ulltickan</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -963,71 +964,70 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111836252</v>
+        <v>130349427</v>
       </c>
       <c r="B5" t="n">
-        <v>89369</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Granåsen, Ång</t>
+          <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607721</v>
+        <v>607743</v>
       </c>
       <c r="R5" t="n">
-        <v>6979452</v>
+        <v>6979551</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1065,71 +1065,74 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111836250</v>
+        <v>129805020</v>
       </c>
       <c r="B6" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Granåsen, Ång</t>
+          <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607694</v>
+        <v>607728</v>
       </c>
       <c r="R6" t="n">
-        <v>6979441</v>
+        <v>6979442</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,12 +1156,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1167,33 +1170,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111836251</v>
+        <v>129916476</v>
       </c>
       <c r="B7" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,37 +1200,44 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Granåsen, Ång</t>
+          <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>607694</v>
+        <v>607670</v>
       </c>
       <c r="R7" t="n">
-        <v>6979441</v>
+        <v>6979437</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1255,12 +1261,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1269,71 +1275,70 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111836257</v>
+        <v>130126081</v>
       </c>
       <c r="B8" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Granåsen, Ång</t>
+          <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>607703</v>
+        <v>607662</v>
       </c>
       <c r="R8" t="n">
-        <v>6979450</v>
+        <v>6979549</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1357,12 +1362,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1371,48 +1376,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111836261</v>
+        <v>130127210</v>
       </c>
       <c r="B9" t="n">
-        <v>81248</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1420,37 +1406,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Granåsen, Ång</t>
+          <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>607662</v>
+        <v>607727</v>
       </c>
       <c r="R9" t="n">
-        <v>6979436</v>
+        <v>6979581</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1474,12 +1463,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1495,27 +1484,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111836249</v>
+        <v>130127284</v>
       </c>
       <c r="B10" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1523,37 +1507,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Granåsen, Ång</t>
+          <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>607657</v>
+        <v>607761</v>
       </c>
       <c r="R10" t="n">
-        <v>6979434</v>
+        <v>6979698</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1577,12 +1564,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1591,71 +1578,70 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111836258</v>
+        <v>130266710</v>
       </c>
       <c r="B11" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Granåsen, Ång</t>
+          <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>607674</v>
+        <v>607751</v>
       </c>
       <c r="R11" t="n">
-        <v>6979540</v>
+        <v>6979617</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1679,12 +1665,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1693,86 +1679,70 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111836255</v>
+        <v>130266801</v>
       </c>
       <c r="B12" t="n">
-        <v>78612</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Granåsen, Ång</t>
+          <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>607703</v>
+        <v>607828</v>
       </c>
       <c r="R12" t="n">
-        <v>6979450</v>
+        <v>6979513</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1796,12 +1766,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1810,86 +1780,70 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111836253</v>
+        <v>130266869</v>
       </c>
       <c r="B13" t="n">
-        <v>78611</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Granåsen, Ång</t>
+          <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>607721</v>
+        <v>607736</v>
       </c>
       <c r="R13" t="n">
-        <v>6979452</v>
+        <v>6979447</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1913,12 +1867,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1927,33 +1881,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111836248</v>
+        <v>130275381</v>
       </c>
       <c r="B14" t="n">
-        <v>73696</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1961,37 +1911,40 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Granåsen, Ång</t>
+          <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>607640</v>
+        <v>607764</v>
       </c>
       <c r="R14" t="n">
-        <v>6979452</v>
+        <v>6979498</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2015,12 +1968,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2029,33 +1982,29 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111836254</v>
+        <v>130306274</v>
       </c>
       <c r="B15" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2063,37 +2012,40 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Granåsen, Ång</t>
+          <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>607721</v>
+        <v>607751</v>
       </c>
       <c r="R15" t="n">
-        <v>6979452</v>
+        <v>6979524</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2117,12 +2069,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Samma låga som rosentickan</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2131,33 +2088,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111836260</v>
+        <v>130349421</v>
       </c>
       <c r="B16" t="n">
-        <v>89462</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2165,37 +2118,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3277</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(O.F.Müll.:Fr.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Granåsen, Ång</t>
+          <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>607637</v>
+        <v>607743</v>
       </c>
       <c r="R16" t="n">
-        <v>6979446</v>
+        <v>6979551</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2219,12 +2175,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-08-05</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2233,33 +2189,29 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111836233</v>
+        <v>130306283</v>
       </c>
       <c r="B17" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2267,37 +2219,40 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Granåsen, Ång</t>
+          <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>607763</v>
+        <v>607751</v>
       </c>
       <c r="R17" t="n">
-        <v>6979468</v>
+        <v>6979524</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2321,12 +2276,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-08-07</t>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Artbestämd efter extern bedömning av foton. Rynkskinn (ungt exemplar) utifrån vit fransig kant och begynnande åsar/rynkor. På grov granlåga tillsammans med ullticka och rosenticka. Ej mikroskoperad.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2335,28 +2295,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Fatima Boukarchid</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129805635</v>
+        <v>111836261</v>
       </c>
       <c r="B18" t="n">
-        <v>57741</v>
+        <v>83173</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2364,49 +2325,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Paljacka, Ång</t>
+          <t>Granåsen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>607700</v>
+        <v>607663</v>
       </c>
       <c r="R18" t="n">
-        <v>6979421</v>
+        <v>6979436</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2430,22 +2379,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>12:13</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:13</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2454,28 +2393,29 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129805053</v>
+        <v>111836260</v>
       </c>
       <c r="B19" t="n">
-        <v>80200</v>
+        <v>92037</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2483,44 +2423,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>3277</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Paljacka, Ång</t>
+          <t>Granåsen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>607694</v>
+        <v>607637</v>
       </c>
       <c r="R19" t="n">
-        <v>6979416</v>
+        <v>6979446</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2544,12 +2477,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2558,83 +2491,66 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129805049</v>
+        <v>111836252</v>
       </c>
       <c r="B20" t="n">
-        <v>57900</v>
+        <v>91872</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Paljacka, Ång</t>
+          <t>Granåsen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>607694</v>
+        <v>607721</v>
       </c>
       <c r="R20" t="n">
-        <v>6979416</v>
+        <v>6979453</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2658,22 +2574,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:58</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:58</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2688,51 +2594,47 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129805020</v>
+        <v>130127255</v>
       </c>
       <c r="B21" t="n">
-        <v>91641</v>
+        <v>91872</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -2742,10 +2644,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>607728</v>
+        <v>607732</v>
       </c>
       <c r="R21" t="n">
-        <v>6979442</v>
+        <v>6979598</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2772,12 +2674,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-12-14</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På undersidan av grenar. Bedömd utifrån foto. Extern input.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,39 +2712,35 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129805111</v>
+        <v>130127479</v>
       </c>
       <c r="B22" t="n">
-        <v>80200</v>
+        <v>91872</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
@@ -2847,10 +2750,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>607710</v>
+        <v>607689</v>
       </c>
       <c r="R22" t="n">
-        <v>6979462</v>
+        <v>6979592</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2877,12 +2780,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-12-14</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På undersidan av grenar. Bedömd utifrån foto. Extern input.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2910,64 +2818,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129917166</v>
+        <v>111836232</v>
       </c>
       <c r="B23" t="n">
-        <v>57007</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Paljacka, Ång</t>
+          <t>Granåsen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>607659</v>
+        <v>607753</v>
       </c>
       <c r="R23" t="n">
-        <v>6979395</v>
+        <v>6979689</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2991,27 +2883,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>12:12</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>12:12</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Stöttes. Totalt 2 ex på olika platser.</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3026,67 +2903,60 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129916476</v>
+        <v>111836233</v>
       </c>
       <c r="B24" t="n">
-        <v>91728</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Paljacka, Ång</t>
+          <t>Granåsen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>607670</v>
+        <v>607763</v>
       </c>
       <c r="R24" t="n">
-        <v>6979437</v>
+        <v>6979468</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3110,12 +2980,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3124,79 +2994,66 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129917143</v>
+        <v>111836249</v>
       </c>
       <c r="B25" t="n">
-        <v>57007</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Paljacka, Ång</t>
+          <t>Granåsen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>607625</v>
+        <v>607657</v>
       </c>
       <c r="R25" t="n">
-        <v>6979416</v>
+        <v>6979434</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3220,27 +3077,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:11</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-11-30</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:11</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Stöttes</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3255,22 +3097,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130127319</v>
+        <v>111836248</v>
       </c>
       <c r="B26" t="n">
-        <v>57852</v>
+        <v>83307</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3278,45 +3120,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Paljacka, Ång</t>
+          <t>Granåsen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>607755</v>
+        <v>607640</v>
       </c>
       <c r="R26" t="n">
-        <v>6979724</v>
+        <v>6979452</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3340,17 +3174,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3365,22 +3194,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130127210</v>
+        <v>111836231</v>
       </c>
       <c r="B27" t="n">
-        <v>91757</v>
+        <v>79946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3388,40 +3217,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Paljacka, Ång</t>
+          <t>Granåsen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>607727</v>
+        <v>607764</v>
       </c>
       <c r="R27" t="n">
-        <v>6979581</v>
+        <v>6979740</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3445,12 +3271,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2023-08-07</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3459,29 +3285,28 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130127284</v>
+        <v>111836251</v>
       </c>
       <c r="B28" t="n">
-        <v>91757</v>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3489,40 +3314,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Paljacka, Ång</t>
+          <t>Granåsen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>607761</v>
+        <v>607694</v>
       </c>
       <c r="R28" t="n">
-        <v>6979698</v>
+        <v>6979441</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3546,12 +3368,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3560,29 +3382,28 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130126081</v>
+        <v>111836254</v>
       </c>
       <c r="B29" t="n">
-        <v>91757</v>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3590,40 +3411,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Paljacka, Ång</t>
+          <t>Granåsen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>607662</v>
+        <v>607721</v>
       </c>
       <c r="R29" t="n">
-        <v>6979549</v>
+        <v>6979453</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3647,12 +3465,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3661,29 +3479,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130126046</v>
+        <v>111836259</v>
       </c>
       <c r="B30" t="n">
-        <v>80314</v>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3709,22 +3526,19 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Paljacka, Ång</t>
+          <t>Granåsen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>607662</v>
+        <v>607667</v>
       </c>
       <c r="R30" t="n">
-        <v>6979549</v>
+        <v>6979558</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3748,12 +3562,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3762,29 +3576,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130127511</v>
+        <v>129805053</v>
       </c>
       <c r="B31" t="n">
-        <v>57033</v>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3792,39 +3605,30 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3832,10 +3636,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>607630</v>
+        <v>607694</v>
       </c>
       <c r="R31" t="n">
-        <v>6979413</v>
+        <v>6979416</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -3862,27 +3666,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Stöttes</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3891,6 +3680,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3909,10 +3699,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130114283</v>
+        <v>129805111</v>
       </c>
       <c r="B32" t="n">
-        <v>91777</v>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3920,29 +3710,29 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
@@ -3951,10 +3741,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>607618</v>
+        <v>607710</v>
       </c>
       <c r="R32" t="n">
-        <v>6979482</v>
+        <v>6979462</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3981,12 +3771,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4014,65 +3804,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130114120</v>
+        <v>130126046</v>
       </c>
       <c r="B33" t="n">
-        <v>58224</v>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>607648</v>
+        <v>607662</v>
       </c>
       <c r="R33" t="n">
-        <v>6979427</v>
+        <v>6979549</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4099,27 +3872,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>11:08</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>11:08</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rörde sig längs marken</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4128,6 +3886,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4146,10 +3905,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130114144</v>
+        <v>130266775</v>
       </c>
       <c r="B34" t="n">
-        <v>57854</v>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4157,46 +3916,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>607648</v>
+        <v>607795</v>
       </c>
       <c r="R34" t="n">
-        <v>6979427</v>
+        <v>6979602</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4223,17 +3973,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>ca 2,5 m över marken.</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4242,6 +3987,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4260,51 +4006,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130266832</v>
+        <v>111836250</v>
       </c>
       <c r="B35" t="n">
-        <v>92072</v>
+        <v>80461</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Paljacka, Ång</t>
+          <t>Granåsen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>607828</v>
+        <v>607694</v>
       </c>
       <c r="R35" t="n">
-        <v>6979513</v>
+        <v>6979441</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4328,12 +4071,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4342,70 +4085,66 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130266710</v>
+        <v>111836256</v>
       </c>
       <c r="B36" t="n">
-        <v>91774</v>
+        <v>80461</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Paljacka, Ång</t>
+          <t>Granåsen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>607751</v>
+        <v>607703</v>
       </c>
       <c r="R36" t="n">
-        <v>6979617</v>
+        <v>6979449</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4429,12 +4168,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4443,70 +4182,81 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130266869</v>
+        <v>111836258</v>
       </c>
       <c r="B37" t="n">
-        <v>91774</v>
+        <v>80461</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Paljacka, Ång</t>
+          <t>Granåsen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>607736</v>
+        <v>607674</v>
       </c>
       <c r="R37" t="n">
-        <v>6979447</v>
+        <v>6979540</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4530,12 +4280,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4544,70 +4294,81 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130266801</v>
+        <v>111836253</v>
       </c>
       <c r="B38" t="n">
-        <v>91774</v>
+        <v>80467</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Paljacka, Ång</t>
+          <t>Granåsen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>607828</v>
+        <v>607721</v>
       </c>
       <c r="R38" t="n">
-        <v>6979513</v>
+        <v>6979453</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4631,12 +4392,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4645,29 +4406,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130238674</v>
+        <v>111836255</v>
       </c>
       <c r="B39" t="n">
-        <v>57966</v>
+        <v>80468</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4675,45 +4435,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103031</v>
+        <v>6464</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Paljacka, Ång</t>
+          <t>Granåsen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>607654</v>
+        <v>607703</v>
       </c>
       <c r="R39" t="n">
-        <v>6979404</v>
+        <v>6979449</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4737,22 +4489,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>11:06</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>11:06</t>
+          <t>2023-08-05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4763,26 +4505,41 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fatima Boukarchid</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130266667</v>
+        <v>129805635</v>
       </c>
       <c r="B40" t="n">
-        <v>92072</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4790,26 +4547,35 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -4817,10 +4583,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>607751</v>
+        <v>607700</v>
       </c>
       <c r="R40" t="n">
-        <v>6979617</v>
+        <v>6979421</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -4847,12 +4613,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4861,7 +4637,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4880,10 +4655,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130275381</v>
+        <v>130114144</v>
       </c>
       <c r="B41" t="n">
-        <v>91774</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4891,37 +4666,46 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>607764</v>
+        <v>607648</v>
       </c>
       <c r="R41" t="n">
-        <v>6979498</v>
+        <v>6979427</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4948,12 +4732,17 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>ca 2,5 m över marken.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4962,7 +4751,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4981,10 +4769,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130276095</v>
+        <v>130127319</v>
       </c>
       <c r="B42" t="n">
-        <v>58021</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4992,50 +4780,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>607828</v>
+        <v>607755</v>
       </c>
       <c r="R42" t="n">
-        <v>6979513</v>
+        <v>6979724</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5062,22 +4842,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>13:25</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>13:25</t>
+          <t>2025-12-14</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5104,37 +4879,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130275701</v>
+        <v>129917143</v>
       </c>
       <c r="B43" t="n">
-        <v>58021</v>
+        <v>57132</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -5144,21 +4919,17 @@
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>607706</v>
+        <v>607625</v>
       </c>
       <c r="R43" t="n">
-        <v>6979662</v>
+        <v>6979416</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5185,27 +4956,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-11-30</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Sannolikt samma fåglar som observerades tidigare. Nyfikna.</t>
+          <t>Stöttes</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5232,10 +5003,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130127479</v>
+        <v>129917166</v>
       </c>
       <c r="B44" t="n">
-        <v>91739</v>
+        <v>57132</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5243,37 +5014,50 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>607689</v>
+        <v>607659</v>
       </c>
       <c r="R44" t="n">
-        <v>6979592</v>
+        <v>6979395</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5300,17 +5084,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-12-14</t>
+          <t>2025-11-30</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På undersidan av grenar. Bedömd utifrån foto. Extern input.</t>
+          <t>Stöttes. Totalt 2 ex på olika platser.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5319,7 +5113,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5338,10 +5131,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130127255</v>
+        <v>130127511</v>
       </c>
       <c r="B45" t="n">
-        <v>91739</v>
+        <v>57132</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5349,26 +5142,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5376,10 +5182,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>607732</v>
+        <v>607630</v>
       </c>
       <c r="R45" t="n">
-        <v>6979598</v>
+        <v>6979413</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5409,14 +5215,24 @@
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-14</t>
         </is>
       </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På undersidan av grenar. Bedömd utifrån foto. Extern input.</t>
+          <t>Stöttes</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5425,7 +5241,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5444,48 +5259,65 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130306278</v>
+        <v>130114120</v>
       </c>
       <c r="B46" t="n">
-        <v>92074</v>
+        <v>58327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>103015</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>607751</v>
+        <v>607648</v>
       </c>
       <c r="R46" t="n">
-        <v>6979524</v>
+        <v>6979427</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5512,17 +5344,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Samma låga som ulltickan</t>
+          <t>Rörde sig längs marken</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5531,7 +5373,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5550,10 +5391,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130266607</v>
+        <v>129805049</v>
       </c>
       <c r="B47" t="n">
-        <v>91796</v>
+        <v>58114</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5561,22 +5402,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
@@ -5584,10 +5442,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>607717</v>
+        <v>607694</v>
       </c>
       <c r="R47" t="n">
-        <v>6979647</v>
+        <v>6979416</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5614,12 +5472,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5628,7 +5496,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5647,10 +5514,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130306274</v>
+        <v>130275468</v>
       </c>
       <c r="B48" t="n">
-        <v>91776</v>
+        <v>58114</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5658,37 +5525,50 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>607751</v>
+        <v>607706</v>
       </c>
       <c r="R48" t="n">
-        <v>6979524</v>
+        <v>6979662</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5715,17 +5595,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Samma låga som rosentickan</t>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5734,7 +5619,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5753,10 +5637,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130306215</v>
+        <v>130276095</v>
       </c>
       <c r="B49" t="n">
-        <v>91796</v>
+        <v>58114</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5764,33 +5648,50 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>607702</v>
+        <v>607828</v>
       </c>
       <c r="R49" t="n">
-        <v>6979571</v>
+        <v>6979513</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -5817,12 +5718,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5831,7 +5742,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5850,37 +5760,42 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130306283</v>
+        <v>130238674</v>
       </c>
       <c r="B50" t="n">
-        <v>92235</v>
+        <v>58057</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1209</v>
+        <v>103031</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
@@ -5888,10 +5803,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>607751</v>
+        <v>607654</v>
       </c>
       <c r="R50" t="n">
-        <v>6979524</v>
+        <v>6979404</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -5918,17 +5833,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Artbestämd efter extern bedömning av foton. Rynkskinn (ungt exemplar) utifrån vit fransig kant och begynnande åsar/rynkor. På grov granlåga tillsammans med ullticka och rosenticka. Ej mikroskoperad.</t>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5937,7 +5857,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5953,208 +5872,6 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>130349421</v>
-      </c>
-      <c r="B51" t="n">
-        <v>91776</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Paljacka, Ång</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>607743</v>
-      </c>
-      <c r="R51" t="n">
-        <v>6979551</v>
-      </c>
-      <c r="S51" t="n">
-        <v>25</v>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V51" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>Graninge</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="AD51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="inlineStr"/>
-      <c r="AG51" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr">
-        <is>
-          <t>Fatima Boukarchid</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>Fatima Boukarchid</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>130349427</v>
-      </c>
-      <c r="B52" t="n">
-        <v>92082</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>658</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Fomitopsis rosea</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>Paljacka, Ång</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>607743</v>
-      </c>
-      <c r="R52" t="n">
-        <v>6979551</v>
-      </c>
-      <c r="S52" t="n">
-        <v>25</v>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>Graninge</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
-        </is>
-      </c>
-      <c r="AD52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF52" t="inlineStr"/>
-      <c r="AG52" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT52" t="inlineStr"/>
-      <c r="AW52" t="inlineStr">
-        <is>
-          <t>Fatima Boukarchid</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>Fatima Boukarchid</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29232-2025 artfynd.xlsx
+++ b/artfynd/A 29232-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AZ50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130266667</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130266832</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130306278</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130349427</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805020</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1291,6 +1321,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129916476</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1392,6 +1427,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130126081</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1493,6 +1533,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130127210</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1594,6 +1639,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130127284</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1695,6 +1745,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130266710</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1796,6 +1851,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130266801</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1897,6 +1957,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130266869</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1998,6 +2063,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130275381</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2104,6 +2174,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130306274</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2205,6 +2280,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130349421</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2311,6 +2391,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130306283</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2409,6 +2494,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111836261</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2506,6 +2596,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111836260</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2603,6 +2698,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111836252</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2709,6 +2809,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130127255</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2815,6 +2920,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130127479</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2912,6 +3022,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111836232</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3009,6 +3124,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111836233</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3106,6 +3226,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111836249</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3203,6 +3328,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111836248</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3300,6 +3430,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111836231</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3397,6 +3532,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111836251</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3494,6 +3634,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111836254</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3591,6 +3736,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111836259</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3696,6 +3846,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805053</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3801,6 +3956,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805111</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3902,6 +4062,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130126046</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4003,6 +4168,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130266775</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4100,6 +4270,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111836250</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4212,6 +4387,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111836256</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4324,6 +4504,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111836258</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4421,6 +4606,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111836253</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4533,6 +4723,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111836255</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4652,6 +4847,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805635</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4766,6 +4966,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130114144</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4876,6 +5081,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130127319</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5000,6 +5210,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129917143</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5128,6 +5343,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129917166</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5256,6 +5476,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130127511</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5388,6 +5613,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130114120</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5511,6 +5741,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129805049</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5634,6 +5869,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130275468</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5757,6 +5997,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130276095</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5872,8 +6117,64 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130238674</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>